--- a/artfynd/A 53665-2025 artfynd.xlsx
+++ b/artfynd/A 53665-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131734452</v>
+        <v>131734367</v>
       </c>
       <c r="B2" t="n">
-        <v>99433</v>
+        <v>95942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lantela Väst, Hls</t>
+          <t>Lantela Nord, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576527</v>
+        <v>576481</v>
       </c>
       <c r="R2" t="n">
-        <v>6896306</v>
+        <v>6896246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131734367</v>
+        <v>131734452</v>
       </c>
       <c r="B3" t="n">
-        <v>95939</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2387</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lantela Nord, Hls</t>
+          <t>Lantela Väst, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576481</v>
+        <v>576527</v>
       </c>
       <c r="R3" t="n">
-        <v>6896246</v>
+        <v>6896306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>131740354</v>
       </c>
       <c r="B4" t="n">
-        <v>101203</v>
+        <v>101206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131739779</v>
       </c>
       <c r="B5" t="n">
-        <v>99119</v>
+        <v>99122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131734556</v>
       </c>
       <c r="B6" t="n">
-        <v>98999</v>
+        <v>99002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131736685</v>
       </c>
       <c r="B7" t="n">
-        <v>96327</v>
+        <v>96330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53665-2025 artfynd.xlsx
+++ b/artfynd/A 53665-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131734367</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>96037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131734452</v>
+        <v>131734475</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lantela Väst, Hls</t>
+          <t>Lantela Nordost, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576527</v>
+        <v>576490</v>
       </c>
       <c r="R3" t="n">
-        <v>6896306</v>
+        <v>6896244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131740354</v>
+        <v>131736685</v>
       </c>
       <c r="B4" t="n">
-        <v>101206</v>
+        <v>96425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>2813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lantela Syd, Hls</t>
+          <t>Lantela Nord, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576550</v>
+        <v>576529</v>
       </c>
       <c r="R4" t="n">
-        <v>6896269</v>
+        <v>6896267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
         <v>131739779</v>
       </c>
       <c r="B5" t="n">
-        <v>99122</v>
+        <v>99219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131734556</v>
+        <v>131734452</v>
       </c>
       <c r="B6" t="n">
-        <v>99002</v>
+        <v>99533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576525</v>
+        <v>576527</v>
       </c>
       <c r="R6" t="n">
-        <v>6896321</v>
+        <v>6896306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131736685</v>
+        <v>131734556</v>
       </c>
       <c r="B7" t="n">
-        <v>96330</v>
+        <v>99099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2813</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lantela Nord, Hls</t>
+          <t>Lantela Väst, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576529</v>
+        <v>576525</v>
       </c>
       <c r="R7" t="n">
-        <v>6896267</v>
+        <v>6896321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1274,309 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131732451</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110023</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220263</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällskråp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Petasites frigidus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lantela Syd, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576603</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6896268</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131733135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lantela Nordost, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576467</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6896231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131740354</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lantela Syd, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576550</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896269</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 53665-2025 artfynd.xlsx
+++ b/artfynd/A 53665-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739779</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734556</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732451</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733135</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>